--- a/data/xlsx/bjma--weaving-and-finishing.xlsx
+++ b/data/xlsx/bjma--weaving-and-finishing.xlsx
@@ -693,7 +693,9 @@
       <c r="C16" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -715,7 +717,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -737,7 +741,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -759,7 +765,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>3</v>
       </c>
@@ -781,7 +789,9 @@
       <c r="C20" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>3</v>
       </c>
@@ -803,7 +813,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>5</v>
       </c>
@@ -825,7 +837,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -847,7 +861,9 @@
       <c r="C23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -869,7 +885,9 @@
       <c r="C24" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -891,7 +909,9 @@
       <c r="C25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -913,7 +933,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -935,7 +957,9 @@
       <c r="C27" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>6</v>
       </c>
@@ -957,7 +981,9 @@
       <c r="C28" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>6</v>
       </c>
@@ -979,7 +1005,9 @@
       <c r="C29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>6</v>
       </c>
@@ -1001,7 +1029,9 @@
       <c r="C30" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>6</v>
       </c>
@@ -1023,7 +1053,9 @@
       <c r="C31" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>7</v>
       </c>
@@ -1045,7 +1077,9 @@
       <c r="C32" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>7</v>
       </c>
@@ -1067,7 +1101,9 @@
       <c r="C33" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>5</v>
       </c>
@@ -1089,7 +1125,9 @@
       <c r="C34" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>7</v>
       </c>
@@ -1111,7 +1149,9 @@
       <c r="C35" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>3</v>
       </c>
@@ -1133,7 +1173,9 @@
       <c r="C36" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>3</v>
       </c>
@@ -1155,7 +1197,9 @@
       <c r="C37" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>3</v>
       </c>
@@ -1177,7 +1221,9 @@
       <c r="C38" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>3</v>
       </c>
@@ -1199,7 +1245,9 @@
       <c r="C39" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>4</v>
       </c>
@@ -1221,7 +1269,9 @@
       <c r="C40" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>6</v>
       </c>
@@ -1243,7 +1293,9 @@
       <c r="C41" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="31" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="31" t="n">
         <v>3</v>
       </c>
@@ -1265,7 +1317,9 @@
       <c r="C42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="31" t="n"/>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="31" t="n">
         <v>5</v>
       </c>
@@ -1287,7 +1341,9 @@
       <c r="C43" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="31" t="n"/>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="31" t="n">
         <v>3</v>
       </c>
@@ -1309,7 +1365,9 @@
       <c r="C44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="31" t="n"/>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="31" t="n">
         <v>5</v>
       </c>
@@ -1331,7 +1389,9 @@
       <c r="C45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="31" t="n"/>
+      <c r="D45" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="31" t="n">
         <v>4</v>
       </c>
@@ -1353,7 +1413,9 @@
       <c r="C46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="31" t="n"/>
+      <c r="D46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="31" t="n">
         <v>3</v>
       </c>
@@ -1375,7 +1437,9 @@
       <c r="C47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="31" t="n"/>
+      <c r="D47" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="31" t="n">
         <v>3</v>
       </c>
